--- a/artfynd/A 28093-2025 artfynd.xlsx
+++ b/artfynd/A 28093-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136092112</v>
       </c>
       <c r="B2" t="n">
-        <v>103074</v>
+        <v>103077</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28093-2025 artfynd.xlsx
+++ b/artfynd/A 28093-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136092112</v>
       </c>
       <c r="B2" t="n">
-        <v>103077</v>
+        <v>103078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
